--- a/reports/tables/Pregnancy_Probability_Tier_Summary_FinalModel_Calibrated.xlsx
+++ b/reports/tables/Pregnancy_Probability_Tier_Summary_FinalModel_Calibrated.xlsx
@@ -487,28 +487,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02293191129993818</v>
+        <v>0.01841834706578366</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0440251572327044</v>
+        <v>0.03409090909090909</v>
       </c>
       <c r="G2" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02941176470588235</v>
+        <v>0.03459119496855346</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.006479853405944175</v>
+        <v>-0.0161728479027698</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -523,28 +523,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1038409443828594</v>
+        <v>0.1087618068204007</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0520792501672002</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1099656357388316</v>
+        <v>0.1075268817204301</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.006124691355972239</v>
+        <v>0.001234925099970544</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
